--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121172744</v>
+        <v>121173036</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>57459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,30 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711136</v>
+        <v>711181</v>
       </c>
       <c r="R6" t="n">
-        <v>7092251</v>
+        <v>7092322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1219,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121173036</v>
+        <v>121172744</v>
       </c>
       <c r="B7" t="n">
-        <v>57459</v>
+        <v>78598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1249,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711181</v>
+        <v>711136</v>
       </c>
       <c r="R7" t="n">
-        <v>7092322</v>
+        <v>7092251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst två</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,6 +1329,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121173043</v>
+        <v>121172849</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711192</v>
+        <v>711238</v>
       </c>
       <c r="R2" t="n">
-        <v>7092394</v>
+        <v>7092305</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121172849</v>
+        <v>121172744</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711238</v>
+        <v>711136</v>
       </c>
       <c r="R3" t="n">
-        <v>7092305</v>
+        <v>7092251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,12 +866,18 @@
           <t>2024-11-13</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,7 +899,7 @@
         <v>121173021</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121172820</v>
+        <v>121173043</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,26 +1023,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711081</v>
+        <v>711192</v>
       </c>
       <c r="R5" t="n">
-        <v>7092245</v>
+        <v>7092394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121173036</v>
+        <v>121172820</v>
       </c>
       <c r="B6" t="n">
-        <v>57459</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711181</v>
+        <v>711081</v>
       </c>
       <c r="R6" t="n">
-        <v>7092322</v>
+        <v>7092245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst två</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121172744</v>
+        <v>121173036</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>57462</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,30 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711136</v>
+        <v>711181</v>
       </c>
       <c r="R7" t="n">
-        <v>7092251</v>
+        <v>7092322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1330,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327847</v>
+        <v>121327951</v>
       </c>
       <c r="B8" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711262</v>
+        <v>711211</v>
       </c>
       <c r="R8" t="n">
-        <v>7092221</v>
+        <v>7092255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327907</v>
+        <v>121327911</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>94749</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,35 +1466,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711207</v>
+        <v>711178</v>
       </c>
       <c r="R9" t="n">
-        <v>7092387</v>
+        <v>7092396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,6 +1542,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1564,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121328034</v>
+        <v>121327907</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,26 +1577,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1607,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711092</v>
+        <v>711207</v>
       </c>
       <c r="R10" t="n">
-        <v>7092202</v>
+        <v>7092387</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1653,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327901</v>
+        <v>121327930</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,25 +1683,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711229</v>
+        <v>711183</v>
       </c>
       <c r="R11" t="n">
-        <v>7092331</v>
+        <v>7092303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,11 +1750,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327839</v>
+        <v>121328022</v>
       </c>
       <c r="B12" t="n">
-        <v>90687</v>
+        <v>79717</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,25 +1789,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711259</v>
+        <v>711065</v>
       </c>
       <c r="R12" t="n">
-        <v>7092208</v>
+        <v>7092292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327925</v>
+        <v>121327941</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,7 +1921,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1935,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711199</v>
+        <v>711196</v>
       </c>
       <c r="R13" t="n">
-        <v>7092314</v>
+        <v>7092277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327930</v>
+        <v>121328042</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>82385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2009,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711183</v>
+        <v>711107</v>
       </c>
       <c r="R14" t="n">
-        <v>7092303</v>
+        <v>7092184</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327883</v>
+        <v>121327981</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,7 +2137,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2151,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711243</v>
+        <v>711115</v>
       </c>
       <c r="R15" t="n">
-        <v>7092325</v>
+        <v>7092280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327981</v>
+        <v>121327892</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,7 +2247,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2261,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711115</v>
+        <v>711222</v>
       </c>
       <c r="R16" t="n">
-        <v>7092280</v>
+        <v>7092349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327911</v>
+        <v>121327839</v>
       </c>
       <c r="B17" t="n">
-        <v>94739</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,31 +2331,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2166</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711178</v>
+        <v>711259</v>
       </c>
       <c r="R17" t="n">
-        <v>7092396</v>
+        <v>7092208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2428,7 @@
         <v>121328016</v>
       </c>
       <c r="B18" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328022</v>
+        <v>121328034</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>79682</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,25 +2543,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711065</v>
+        <v>711092</v>
       </c>
       <c r="R19" t="n">
-        <v>7092292</v>
+        <v>7092202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327892</v>
+        <v>121327967</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,31 +2653,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711222</v>
+        <v>711127</v>
       </c>
       <c r="R20" t="n">
-        <v>7092349</v>
+        <v>7092343</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,6 +2724,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2752,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121328042</v>
+        <v>121327925</v>
       </c>
       <c r="B21" t="n">
-        <v>82382</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,26 +2759,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2795,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711107</v>
+        <v>711199</v>
       </c>
       <c r="R21" t="n">
-        <v>7092184</v>
+        <v>7092314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2839,7 +2835,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2858,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327967</v>
+        <v>121327883</v>
       </c>
       <c r="B22" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,26 +2869,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711127</v>
+        <v>711243</v>
       </c>
       <c r="R22" t="n">
-        <v>7092343</v>
+        <v>7092325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2945,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327941</v>
+        <v>121327847</v>
       </c>
       <c r="B23" t="n">
-        <v>57348</v>
+        <v>82385</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,31 +2979,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3012,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711196</v>
+        <v>711262</v>
       </c>
       <c r="R23" t="n">
-        <v>7092277</v>
+        <v>7092221</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,6 +3050,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3074,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121328046</v>
+        <v>121327901</v>
       </c>
       <c r="B24" t="n">
-        <v>57501</v>
+        <v>79711</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,35 +3081,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3122,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711126</v>
+        <v>711229</v>
       </c>
       <c r="R24" t="n">
-        <v>7092192</v>
+        <v>7092331</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,12 +3150,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3187,7 +3183,7 @@
         <v>121327974</v>
       </c>
       <c r="B25" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3290,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327951</v>
+        <v>121328046</v>
       </c>
       <c r="B26" t="n">
-        <v>82382</v>
+        <v>57504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,26 +3302,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3333,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711211</v>
+        <v>711126</v>
       </c>
       <c r="R26" t="n">
-        <v>7092255</v>
+        <v>7092192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3378,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -2531,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328034</v>
+        <v>121327967</v>
       </c>
       <c r="B19" t="n">
-        <v>79682</v>
+        <v>90715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711092</v>
+        <v>711127</v>
       </c>
       <c r="R19" t="n">
-        <v>7092202</v>
+        <v>7092343</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327967</v>
+        <v>121328034</v>
       </c>
       <c r="B20" t="n">
-        <v>90715</v>
+        <v>79682</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711127</v>
+        <v>711092</v>
       </c>
       <c r="R20" t="n">
-        <v>7092343</v>
+        <v>7092202</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121172849</v>
+        <v>121173021</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711238</v>
+        <v>711216</v>
       </c>
       <c r="R2" t="n">
-        <v>7092305</v>
+        <v>7092369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +756,18 @@
           <t>2024-11-13</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121172744</v>
+        <v>121173044</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711136</v>
+        <v>711192</v>
       </c>
       <c r="R3" t="n">
-        <v>7092251</v>
+        <v>7092394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121173021</v>
+        <v>121172820</v>
       </c>
       <c r="B4" t="n">
         <v>79682</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711216</v>
+        <v>711081</v>
       </c>
       <c r="R4" t="n">
-        <v>7092369</v>
+        <v>7092245</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121173043</v>
+        <v>121173036</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57462</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,20 +1024,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1040,14 +1045,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711192</v>
+        <v>711181</v>
       </c>
       <c r="R5" t="n">
-        <v>7092394</v>
+        <v>7092322</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121172820</v>
+        <v>121172849</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,26 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711081</v>
+        <v>711238</v>
       </c>
       <c r="R6" t="n">
-        <v>7092245</v>
+        <v>7092305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,18 +1213,12 @@
           <t>2024-11-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på sälg</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121173036</v>
+        <v>121172744</v>
       </c>
       <c r="B7" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1249,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711181</v>
+        <v>711136</v>
       </c>
       <c r="R7" t="n">
-        <v>7092322</v>
+        <v>7092251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst två</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,6 +1329,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327951</v>
+        <v>121327911</v>
       </c>
       <c r="B8" t="n">
-        <v>82385</v>
+        <v>94749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,30 +1360,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711211</v>
+        <v>711178</v>
       </c>
       <c r="R8" t="n">
-        <v>7092255</v>
+        <v>7092396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327911</v>
+        <v>121327967</v>
       </c>
       <c r="B9" t="n">
-        <v>94749</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,31 +1467,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2166</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711178</v>
+        <v>711127</v>
       </c>
       <c r="R9" t="n">
-        <v>7092396</v>
+        <v>7092343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327907</v>
+        <v>121328022</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>79717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,35 +1573,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711207</v>
+        <v>711065</v>
       </c>
       <c r="R10" t="n">
-        <v>7092387</v>
+        <v>7092292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,6 +1648,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1671,10 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327930</v>
+        <v>121327892</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,26 +1683,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711183</v>
+        <v>711222</v>
       </c>
       <c r="R11" t="n">
-        <v>7092303</v>
+        <v>7092349</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1759,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121328022</v>
+        <v>121327981</v>
       </c>
       <c r="B12" t="n">
-        <v>79717</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,30 +1789,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1820,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711065</v>
+        <v>711115</v>
       </c>
       <c r="R12" t="n">
-        <v>7092292</v>
+        <v>7092280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1869,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327941</v>
+        <v>121328046</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,31 +1903,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1931,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711196</v>
+        <v>711126</v>
       </c>
       <c r="R13" t="n">
-        <v>7092277</v>
+        <v>7092192</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327981</v>
+        <v>121327839</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,31 +2119,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2147,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711115</v>
+        <v>711259</v>
       </c>
       <c r="R15" t="n">
-        <v>7092280</v>
+        <v>7092208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,6 +2190,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327892</v>
+        <v>121327907</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711222</v>
+        <v>711207</v>
       </c>
       <c r="R16" t="n">
-        <v>7092349</v>
+        <v>7092387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327839</v>
+        <v>121327951</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>82385</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711259</v>
+        <v>711211</v>
       </c>
       <c r="R17" t="n">
-        <v>7092208</v>
+        <v>7092255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327967</v>
+        <v>121327974</v>
       </c>
       <c r="B19" t="n">
-        <v>90715</v>
+        <v>79682</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711127</v>
+        <v>711057</v>
       </c>
       <c r="R19" t="n">
-        <v>7092343</v>
+        <v>7092348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121328034</v>
+        <v>121327901</v>
       </c>
       <c r="B20" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711092</v>
+        <v>711229</v>
       </c>
       <c r="R20" t="n">
-        <v>7092202</v>
+        <v>7092331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,6 +2716,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327883</v>
+        <v>121328034</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>79682</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,31 +2874,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711243</v>
+        <v>711092</v>
       </c>
       <c r="R22" t="n">
-        <v>7092325</v>
+        <v>7092202</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,6 +2945,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2963,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327847</v>
+        <v>121327941</v>
       </c>
       <c r="B23" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,26 +2980,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3006,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711262</v>
+        <v>711196</v>
       </c>
       <c r="R23" t="n">
-        <v>7092221</v>
+        <v>7092277</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3050,7 +3056,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3069,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327901</v>
+        <v>121327847</v>
       </c>
       <c r="B24" t="n">
-        <v>79711</v>
+        <v>82385</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3112,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711229</v>
+        <v>711262</v>
       </c>
       <c r="R24" t="n">
-        <v>7092331</v>
+        <v>7092221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3148,11 +3153,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327974</v>
+        <v>121327930</v>
       </c>
       <c r="B25" t="n">
         <v>79682</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711057</v>
+        <v>711183</v>
       </c>
       <c r="R25" t="n">
-        <v>7092348</v>
+        <v>7092303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121328046</v>
+        <v>121327883</v>
       </c>
       <c r="B26" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,31 +3302,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711126</v>
+        <v>711243</v>
       </c>
       <c r="R26" t="n">
-        <v>7092192</v>
+        <v>7092325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Severin Suess, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Severin Suess</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121173021</v>
+        <v>121173044</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711216</v>
+        <v>711192</v>
       </c>
       <c r="R2" t="n">
-        <v>7092369</v>
+        <v>7092394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Mycket</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121173044</v>
+        <v>121173021</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711192</v>
+        <v>711216</v>
       </c>
       <c r="R3" t="n">
-        <v>7092394</v>
+        <v>7092369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Mycket</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121172820</v>
+        <v>121172849</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,26 +917,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711081</v>
+        <v>711238</v>
       </c>
       <c r="R4" t="n">
-        <v>7092245</v>
+        <v>7092305</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,18 +987,12 @@
           <t>2024-11-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på sälg</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121172849</v>
+        <v>121172744</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,31 +1142,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711238</v>
+        <v>711136</v>
       </c>
       <c r="R6" t="n">
-        <v>7092305</v>
+        <v>7092251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,12 +1207,18 @@
           <t>2024-11-13</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121172744</v>
+        <v>121172820</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711136</v>
+        <v>711081</v>
       </c>
       <c r="R7" t="n">
-        <v>7092251</v>
+        <v>7092245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327911</v>
+        <v>121327967</v>
       </c>
       <c r="B8" t="n">
-        <v>94749</v>
+        <v>90727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,31 +1360,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2166</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711178</v>
+        <v>711127</v>
       </c>
       <c r="R8" t="n">
-        <v>7092396</v>
+        <v>7092343</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327967</v>
+        <v>121327901</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>79714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711127</v>
+        <v>711229</v>
       </c>
       <c r="R9" t="n">
-        <v>7092343</v>
+        <v>7092331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,6 +1533,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121328022</v>
+        <v>121327981</v>
       </c>
       <c r="B10" t="n">
-        <v>79717</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,30 +1577,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1604,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711065</v>
+        <v>711115</v>
       </c>
       <c r="R10" t="n">
-        <v>7092292</v>
+        <v>7092280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,7 +1657,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327892</v>
+        <v>121327951</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>82388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,31 +1691,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711222</v>
+        <v>711211</v>
       </c>
       <c r="R11" t="n">
-        <v>7092349</v>
+        <v>7092255</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1762,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1781,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327981</v>
+        <v>121327941</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1825,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711115</v>
+        <v>711196</v>
       </c>
       <c r="R12" t="n">
-        <v>7092280</v>
+        <v>7092277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121328046</v>
+        <v>121327847</v>
       </c>
       <c r="B13" t="n">
-        <v>57504</v>
+        <v>82388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,31 +1907,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1935,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711126</v>
+        <v>711262</v>
       </c>
       <c r="R13" t="n">
-        <v>7092192</v>
+        <v>7092221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121328042</v>
+        <v>121327883</v>
       </c>
       <c r="B14" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,26 +2013,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2040,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711107</v>
+        <v>711243</v>
       </c>
       <c r="R14" t="n">
-        <v>7092184</v>
+        <v>7092325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2089,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2106,7 +2110,7 @@
         <v>121327839</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327907</v>
+        <v>121327974</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,31 +2229,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2257,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711207</v>
+        <v>711057</v>
       </c>
       <c r="R16" t="n">
-        <v>7092387</v>
+        <v>7092348</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,6 +2300,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327951</v>
+        <v>121327925</v>
       </c>
       <c r="B17" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,26 +2335,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711211</v>
+        <v>711199</v>
       </c>
       <c r="R17" t="n">
-        <v>7092255</v>
+        <v>7092314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2411,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2425,10 +2429,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121328016</v>
+        <v>121327930</v>
       </c>
       <c r="B18" t="n">
-        <v>82385</v>
+        <v>79685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,21 +2445,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711061</v>
+        <v>711183</v>
       </c>
       <c r="R18" t="n">
-        <v>7092314</v>
+        <v>7092303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327974</v>
+        <v>121328016</v>
       </c>
       <c r="B19" t="n">
-        <v>79682</v>
+        <v>82388</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,21 +2551,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711057</v>
+        <v>711061</v>
       </c>
       <c r="R19" t="n">
-        <v>7092348</v>
+        <v>7092314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327901</v>
+        <v>121328034</v>
       </c>
       <c r="B20" t="n">
-        <v>79711</v>
+        <v>79685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2649,25 +2653,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711229</v>
+        <v>711092</v>
       </c>
       <c r="R20" t="n">
-        <v>7092331</v>
+        <v>7092202</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,11 +2720,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,10 +2747,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327925</v>
+        <v>121328022</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>79720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,35 +2759,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2796,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711199</v>
+        <v>711065</v>
       </c>
       <c r="R21" t="n">
-        <v>7092314</v>
+        <v>7092292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,6 +2834,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2858,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121328034</v>
+        <v>121328046</v>
       </c>
       <c r="B22" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,26 +2869,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711092</v>
+        <v>711126</v>
       </c>
       <c r="R22" t="n">
-        <v>7092202</v>
+        <v>7092192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2945,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327941</v>
+        <v>121328042</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>82388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,31 +2979,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3012,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711196</v>
+        <v>711107</v>
       </c>
       <c r="R23" t="n">
-        <v>7092277</v>
+        <v>7092184</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,6 +3050,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3074,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327847</v>
+        <v>121327911</v>
       </c>
       <c r="B24" t="n">
-        <v>82385</v>
+        <v>94761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,30 +3081,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3113,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711262</v>
+        <v>711178</v>
       </c>
       <c r="R24" t="n">
-        <v>7092221</v>
+        <v>7092396</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327930</v>
+        <v>121327907</v>
       </c>
       <c r="B25" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,26 +3192,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3223,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711183</v>
+        <v>711207</v>
       </c>
       <c r="R25" t="n">
-        <v>7092303</v>
+        <v>7092387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3267,7 +3268,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327883</v>
+        <v>121327892</v>
       </c>
       <c r="B26" t="n">
         <v>57351</v>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711243</v>
+        <v>711222</v>
       </c>
       <c r="R26" t="n">
-        <v>7092325</v>
+        <v>7092349</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Severin Suess</t>
+          <t>Severin Suess, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121173044</v>
+        <v>121173036</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57462</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711192</v>
+        <v>711181</v>
       </c>
       <c r="R2" t="n">
-        <v>7092394</v>
+        <v>7092322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121173021</v>
+        <v>121172820</v>
       </c>
       <c r="B3" t="n">
         <v>79685</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711216</v>
+        <v>711081</v>
       </c>
       <c r="R3" t="n">
-        <v>7092369</v>
+        <v>7092245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121172849</v>
+        <v>121173044</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711238</v>
+        <v>711192</v>
       </c>
       <c r="R4" t="n">
-        <v>7092305</v>
+        <v>7092394</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,6 +985,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121173036</v>
+        <v>121172849</v>
       </c>
       <c r="B5" t="n">
-        <v>57462</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1028,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,14 +1049,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711181</v>
+        <v>711238</v>
       </c>
       <c r="R5" t="n">
-        <v>7092322</v>
+        <v>7092305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,11 +1100,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst två</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121172744</v>
+        <v>121173021</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711136</v>
+        <v>711216</v>
       </c>
       <c r="R6" t="n">
-        <v>7092251</v>
+        <v>7092369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121172820</v>
+        <v>121172744</v>
       </c>
       <c r="B7" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711081</v>
+        <v>711136</v>
       </c>
       <c r="R7" t="n">
-        <v>7092245</v>
+        <v>7092251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327967</v>
+        <v>121327911</v>
       </c>
       <c r="B8" t="n">
-        <v>90727</v>
+        <v>94762</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,30 +1360,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2166</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711127</v>
+        <v>711178</v>
       </c>
       <c r="R8" t="n">
-        <v>7092343</v>
+        <v>7092396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327901</v>
+        <v>121328034</v>
       </c>
       <c r="B9" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711229</v>
+        <v>711092</v>
       </c>
       <c r="R9" t="n">
-        <v>7092331</v>
+        <v>7092202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,11 +1534,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327981</v>
+        <v>121327901</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>79714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,35 +1573,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711115</v>
+        <v>711229</v>
       </c>
       <c r="R10" t="n">
-        <v>7092280</v>
+        <v>7092331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,12 +1642,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1781,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327941</v>
+        <v>121328022</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>79720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,35 +1790,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1829,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711196</v>
+        <v>711065</v>
       </c>
       <c r="R12" t="n">
-        <v>7092277</v>
+        <v>7092292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,6 +1865,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1891,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327847</v>
+        <v>121327930</v>
       </c>
       <c r="B13" t="n">
-        <v>82388</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1900,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711262</v>
+        <v>711183</v>
       </c>
       <c r="R13" t="n">
-        <v>7092221</v>
+        <v>7092303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327883</v>
+        <v>121327967</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,31 +2006,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2045,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711243</v>
+        <v>711127</v>
       </c>
       <c r="R14" t="n">
-        <v>7092325</v>
+        <v>7092343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,6 +2077,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2107,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327839</v>
+        <v>121327907</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,26 +2112,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2150,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711259</v>
+        <v>711207</v>
       </c>
       <c r="R15" t="n">
-        <v>7092208</v>
+        <v>7092387</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,7 +2188,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2213,10 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327974</v>
+        <v>121327892</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,26 +2222,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2256,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711057</v>
+        <v>711222</v>
       </c>
       <c r="R16" t="n">
-        <v>7092348</v>
+        <v>7092349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,7 +2298,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2319,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327925</v>
+        <v>121328046</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,31 +2332,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2367,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711199</v>
+        <v>711126</v>
       </c>
       <c r="R17" t="n">
-        <v>7092314</v>
+        <v>7092192</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327930</v>
+        <v>121328042</v>
       </c>
       <c r="B18" t="n">
-        <v>79685</v>
+        <v>82388</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,21 +2442,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711183</v>
+        <v>711107</v>
       </c>
       <c r="R18" t="n">
-        <v>7092303</v>
+        <v>7092184</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2535,10 +2532,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328016</v>
+        <v>121327974</v>
       </c>
       <c r="B19" t="n">
-        <v>82388</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,21 +2548,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711061</v>
+        <v>711057</v>
       </c>
       <c r="R19" t="n">
-        <v>7092314</v>
+        <v>7092348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,10 +2638,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121328034</v>
+        <v>121327839</v>
       </c>
       <c r="B20" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,21 +2654,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711092</v>
+        <v>711259</v>
       </c>
       <c r="R20" t="n">
-        <v>7092202</v>
+        <v>7092208</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121328022</v>
+        <v>121327925</v>
       </c>
       <c r="B21" t="n">
-        <v>79720</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2759,30 +2756,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2790,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711065</v>
+        <v>711199</v>
       </c>
       <c r="R21" t="n">
-        <v>7092292</v>
+        <v>7092314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,7 +2836,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2853,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121328046</v>
+        <v>121327847</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>82388</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,31 +2870,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711126</v>
+        <v>711262</v>
       </c>
       <c r="R22" t="n">
-        <v>7092192</v>
+        <v>7092221</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,6 +2941,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2963,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121328042</v>
+        <v>121328016</v>
       </c>
       <c r="B23" t="n">
         <v>82388</v>
@@ -3006,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711107</v>
+        <v>711061</v>
       </c>
       <c r="R23" t="n">
-        <v>7092184</v>
+        <v>7092314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327911</v>
+        <v>121327883</v>
       </c>
       <c r="B24" t="n">
-        <v>94761</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,31 +3078,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2166</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3113,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711178</v>
+        <v>711243</v>
       </c>
       <c r="R24" t="n">
-        <v>7092396</v>
+        <v>7092325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,7 +3158,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327907</v>
+        <v>121327981</v>
       </c>
       <c r="B25" t="n">
         <v>57351</v>
@@ -3214,7 +3214,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711207</v>
+        <v>711115</v>
       </c>
       <c r="R25" t="n">
-        <v>7092387</v>
+        <v>7092280</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327892</v>
+        <v>121327941</v>
       </c>
       <c r="B26" t="n">
         <v>57351</v>
@@ -3324,7 +3324,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711222</v>
+        <v>711196</v>
       </c>
       <c r="R26" t="n">
-        <v>7092349</v>
+        <v>7092277</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121173036</v>
+        <v>121172820</v>
       </c>
       <c r="B2" t="n">
-        <v>57462</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711181</v>
+        <v>711081</v>
       </c>
       <c r="R2" t="n">
-        <v>7092322</v>
+        <v>7092245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst två</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121172820</v>
+        <v>121173036</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>57465</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711081</v>
+        <v>711181</v>
       </c>
       <c r="R3" t="n">
-        <v>7092245</v>
+        <v>7092322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121173044</v>
+        <v>121173021</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,31 +917,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711192</v>
+        <v>711216</v>
       </c>
       <c r="R4" t="n">
-        <v>7092394</v>
+        <v>7092369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Mycket</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121172849</v>
+        <v>121173044</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1028,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1064,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711238</v>
+        <v>711192</v>
       </c>
       <c r="R5" t="n">
-        <v>7092305</v>
+        <v>7092394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121173021</v>
+        <v>121172744</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711216</v>
+        <v>711136</v>
       </c>
       <c r="R6" t="n">
-        <v>7092369</v>
+        <v>7092251</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1210,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mycket</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121172744</v>
+        <v>121172849</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711136</v>
+        <v>711238</v>
       </c>
       <c r="R7" t="n">
-        <v>7092251</v>
+        <v>7092305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,18 +1324,12 @@
           <t>2024-11-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327911</v>
+        <v>121327951</v>
       </c>
       <c r="B8" t="n">
-        <v>94762</v>
+        <v>82391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,31 +1360,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2166</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711178</v>
+        <v>711211</v>
       </c>
       <c r="R8" t="n">
-        <v>7092396</v>
+        <v>7092255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121328034</v>
+        <v>121327941</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,26 +1470,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711092</v>
+        <v>711196</v>
       </c>
       <c r="R9" t="n">
-        <v>7092202</v>
+        <v>7092277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1546,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1561,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327901</v>
+        <v>121327911</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>94765</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,26 +1580,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2166</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1604,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711229</v>
+        <v>711178</v>
       </c>
       <c r="R10" t="n">
-        <v>7092331</v>
+        <v>7092396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,11 +1644,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327951</v>
+        <v>121327907</v>
       </c>
       <c r="B11" t="n">
-        <v>82388</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,26 +1687,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711211</v>
+        <v>711207</v>
       </c>
       <c r="R11" t="n">
-        <v>7092255</v>
+        <v>7092387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1763,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1778,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121328022</v>
+        <v>121328042</v>
       </c>
       <c r="B12" t="n">
-        <v>79720</v>
+        <v>82391</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,25 +1793,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711065</v>
+        <v>711107</v>
       </c>
       <c r="R12" t="n">
-        <v>7092292</v>
+        <v>7092184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327930</v>
+        <v>121327925</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,26 +1903,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711183</v>
+        <v>711199</v>
       </c>
       <c r="R13" t="n">
-        <v>7092303</v>
+        <v>7092314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1979,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1990,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327967</v>
+        <v>121327981</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,26 +2013,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2033,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711127</v>
+        <v>711115</v>
       </c>
       <c r="R14" t="n">
-        <v>7092343</v>
+        <v>7092280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2089,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2096,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327907</v>
+        <v>121327930</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>79688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,31 +2123,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2144,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711207</v>
+        <v>711183</v>
       </c>
       <c r="R15" t="n">
-        <v>7092387</v>
+        <v>7092303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,6 +2194,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2206,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327892</v>
+        <v>121327974</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,31 +2229,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2254,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711222</v>
+        <v>711057</v>
       </c>
       <c r="R16" t="n">
-        <v>7092349</v>
+        <v>7092348</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,6 +2300,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121328046</v>
+        <v>121327883</v>
       </c>
       <c r="B17" t="n">
-        <v>57504</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,31 +2335,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2364,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711126</v>
+        <v>711243</v>
       </c>
       <c r="R17" t="n">
-        <v>7092192</v>
+        <v>7092325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,10 +2429,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121328042</v>
+        <v>121328046</v>
       </c>
       <c r="B18" t="n">
-        <v>82388</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,26 +2445,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2469,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711107</v>
+        <v>711126</v>
       </c>
       <c r="R18" t="n">
-        <v>7092184</v>
+        <v>7092192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2521,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2532,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327974</v>
+        <v>121327901</v>
       </c>
       <c r="B19" t="n">
-        <v>79685</v>
+        <v>79717</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2544,25 +2551,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2575,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711057</v>
+        <v>711229</v>
       </c>
       <c r="R19" t="n">
-        <v>7092348</v>
+        <v>7092331</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,6 +2618,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327839</v>
+        <v>121328022</v>
       </c>
       <c r="B20" t="n">
-        <v>90710</v>
+        <v>79723</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2650,25 +2662,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711259</v>
+        <v>711065</v>
       </c>
       <c r="R20" t="n">
-        <v>7092208</v>
+        <v>7092292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327925</v>
+        <v>121328016</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>82391</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,31 +2772,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2792,7 +2799,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711199</v>
+        <v>711061</v>
       </c>
       <c r="R21" t="n">
         <v>7092314</v>
@@ -2836,6 +2843,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2854,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327847</v>
+        <v>121327839</v>
       </c>
       <c r="B22" t="n">
-        <v>82388</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2897,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711262</v>
+        <v>711259</v>
       </c>
       <c r="R22" t="n">
-        <v>7092221</v>
+        <v>7092208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121328016</v>
+        <v>121328034</v>
       </c>
       <c r="B23" t="n">
-        <v>82388</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2976,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711061</v>
+        <v>711092</v>
       </c>
       <c r="R23" t="n">
-        <v>7092314</v>
+        <v>7092202</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327883</v>
+        <v>121327967</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,31 +3090,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3114,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711243</v>
+        <v>711127</v>
       </c>
       <c r="R24" t="n">
-        <v>7092325</v>
+        <v>7092343</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,6 +3161,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3176,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327981</v>
+        <v>121327847</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>82391</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,31 +3196,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3224,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711115</v>
+        <v>711262</v>
       </c>
       <c r="R25" t="n">
-        <v>7092280</v>
+        <v>7092221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,6 +3267,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327941</v>
+        <v>121327892</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711196</v>
+        <v>711222</v>
       </c>
       <c r="R26" t="n">
-        <v>7092277</v>
+        <v>7092349</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121172820</v>
+        <v>121173043</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711081</v>
+        <v>711192</v>
       </c>
       <c r="R2" t="n">
-        <v>7092245</v>
+        <v>7092394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121173036</v>
+        <v>121172849</v>
       </c>
       <c r="B3" t="n">
-        <v>57465</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +802,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,14 +823,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711181</v>
+        <v>711238</v>
       </c>
       <c r="R3" t="n">
-        <v>7092322</v>
+        <v>7092305</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst två</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121173021</v>
+        <v>121173036</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>57465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,30 +912,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711216</v>
+        <v>711181</v>
       </c>
       <c r="R4" t="n">
-        <v>7092369</v>
+        <v>7092322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121173044</v>
+        <v>121172820</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1031,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711192</v>
+        <v>711081</v>
       </c>
       <c r="R5" t="n">
-        <v>7092394</v>
+        <v>7092245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1107,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121172849</v>
+        <v>121173021</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,31 +1253,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711238</v>
+        <v>711216</v>
       </c>
       <c r="R7" t="n">
-        <v>7092305</v>
+        <v>7092369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,12 +1318,18 @@
           <t>2024-11-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327951</v>
+        <v>121328022</v>
       </c>
       <c r="B8" t="n">
-        <v>82391</v>
+        <v>79723</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711211</v>
+        <v>711065</v>
       </c>
       <c r="R8" t="n">
-        <v>7092255</v>
+        <v>7092292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327941</v>
+        <v>121327901</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>79717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,35 +1466,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711196</v>
+        <v>711229</v>
       </c>
       <c r="R9" t="n">
-        <v>7092277</v>
+        <v>7092331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,12 +1535,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1564,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327911</v>
+        <v>121327981</v>
       </c>
       <c r="B10" t="n">
-        <v>94765</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,31 +1577,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2166</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711178</v>
+        <v>711115</v>
       </c>
       <c r="R10" t="n">
-        <v>7092396</v>
+        <v>7092280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1657,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1671,7 +1675,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327907</v>
+        <v>121327925</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1719,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711207</v>
+        <v>711199</v>
       </c>
       <c r="R11" t="n">
-        <v>7092387</v>
+        <v>7092314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121328042</v>
+        <v>121327839</v>
       </c>
       <c r="B12" t="n">
-        <v>82391</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711107</v>
+        <v>711259</v>
       </c>
       <c r="R12" t="n">
-        <v>7092184</v>
+        <v>7092208</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327925</v>
+        <v>121328034</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>79688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,31 +1907,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1935,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711199</v>
+        <v>711092</v>
       </c>
       <c r="R13" t="n">
-        <v>7092314</v>
+        <v>7092202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327981</v>
+        <v>121327911</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>94765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,35 +2009,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2166</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2045,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711115</v>
+        <v>711178</v>
       </c>
       <c r="R14" t="n">
-        <v>7092280</v>
+        <v>7092396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,6 +2085,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2107,10 +2104,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327930</v>
+        <v>121328016</v>
       </c>
       <c r="B15" t="n">
-        <v>79688</v>
+        <v>82391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,21 +2120,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711183</v>
+        <v>711061</v>
       </c>
       <c r="R15" t="n">
-        <v>7092303</v>
+        <v>7092314</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327974</v>
+        <v>121328042</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>82391</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,21 +2226,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711057</v>
+        <v>711107</v>
       </c>
       <c r="R16" t="n">
-        <v>7092348</v>
+        <v>7092184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327883</v>
+        <v>121327847</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,31 +2332,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2367,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711243</v>
+        <v>711262</v>
       </c>
       <c r="R17" t="n">
-        <v>7092325</v>
+        <v>7092221</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,6 +2403,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2429,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121328046</v>
+        <v>121327967</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>90731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,31 +2438,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2477,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711126</v>
+        <v>711127</v>
       </c>
       <c r="R18" t="n">
-        <v>7092192</v>
+        <v>7092343</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,6 +2509,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2539,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327901</v>
+        <v>121327951</v>
       </c>
       <c r="B19" t="n">
-        <v>79717</v>
+        <v>82391</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,25 +2540,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,10 +2571,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711229</v>
+        <v>711211</v>
       </c>
       <c r="R19" t="n">
-        <v>7092331</v>
+        <v>7092255</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,11 +2607,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,10 +2634,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121328022</v>
+        <v>121327907</v>
       </c>
       <c r="B20" t="n">
-        <v>79723</v>
+        <v>57354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,30 +2646,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2693,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711065</v>
+        <v>711207</v>
       </c>
       <c r="R20" t="n">
-        <v>7092292</v>
+        <v>7092387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,7 +2726,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2756,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121328016</v>
+        <v>121327892</v>
       </c>
       <c r="B21" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,26 +2760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2799,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711061</v>
+        <v>711222</v>
       </c>
       <c r="R21" t="n">
-        <v>7092314</v>
+        <v>7092349</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2836,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2862,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327839</v>
+        <v>121327883</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2878,26 +2870,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2905,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711259</v>
+        <v>711243</v>
       </c>
       <c r="R22" t="n">
-        <v>7092208</v>
+        <v>7092325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,7 +2946,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2968,7 +2964,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121328034</v>
+        <v>121327930</v>
       </c>
       <c r="B23" t="n">
         <v>79688</v>
@@ -3011,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711092</v>
+        <v>711183</v>
       </c>
       <c r="R23" t="n">
-        <v>7092202</v>
+        <v>7092303</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327967</v>
+        <v>121327974</v>
       </c>
       <c r="B24" t="n">
-        <v>90731</v>
+        <v>79688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3113,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711127</v>
+        <v>711057</v>
       </c>
       <c r="R24" t="n">
-        <v>7092343</v>
+        <v>7092348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327847</v>
+        <v>121327941</v>
       </c>
       <c r="B25" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,26 +3192,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3223,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711262</v>
+        <v>711196</v>
       </c>
       <c r="R25" t="n">
-        <v>7092221</v>
+        <v>7092277</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3267,7 +3268,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327892</v>
+        <v>121328046</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,31 +3302,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711222</v>
+        <v>711126</v>
       </c>
       <c r="R26" t="n">
-        <v>7092349</v>
+        <v>7092192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -2316,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327847</v>
+        <v>121327967</v>
       </c>
       <c r="B17" t="n">
-        <v>82391</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711262</v>
+        <v>711127</v>
       </c>
       <c r="R17" t="n">
-        <v>7092221</v>
+        <v>7092343</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327967</v>
+        <v>121327847</v>
       </c>
       <c r="B18" t="n">
-        <v>90731</v>
+        <v>82391</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711127</v>
+        <v>711262</v>
       </c>
       <c r="R18" t="n">
-        <v>7092343</v>
+        <v>7092221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327839</v>
+        <v>121328034</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711259</v>
+        <v>711092</v>
       </c>
       <c r="R12" t="n">
-        <v>7092208</v>
+        <v>7092202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121328034</v>
+        <v>121327839</v>
       </c>
       <c r="B13" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711092</v>
+        <v>711259</v>
       </c>
       <c r="R13" t="n">
-        <v>7092202</v>
+        <v>7092208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327967</v>
+        <v>121327847</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>82391</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711127</v>
+        <v>711262</v>
       </c>
       <c r="R17" t="n">
-        <v>7092343</v>
+        <v>7092221</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327847</v>
+        <v>121327967</v>
       </c>
       <c r="B18" t="n">
-        <v>82391</v>
+        <v>90731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711262</v>
+        <v>711127</v>
       </c>
       <c r="R18" t="n">
-        <v>7092221</v>
+        <v>7092343</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121173043</v>
+        <v>121172820</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711192</v>
+        <v>711081</v>
       </c>
       <c r="R2" t="n">
-        <v>7092394</v>
+        <v>7092245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,7 +789,7 @@
         <v>121172849</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121173036</v>
+        <v>121173021</v>
       </c>
       <c r="B4" t="n">
-        <v>57465</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711181</v>
+        <v>711216</v>
       </c>
       <c r="R4" t="n">
-        <v>7092322</v>
+        <v>7092369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst två</t>
+          <t>Mycket</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121172820</v>
+        <v>121173043</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,26 +1023,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711081</v>
+        <v>711192</v>
       </c>
       <c r="R5" t="n">
-        <v>7092245</v>
+        <v>7092394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1125,7 @@
         <v>121172744</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121173021</v>
+        <v>121173036</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>57466</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,30 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711216</v>
+        <v>711181</v>
       </c>
       <c r="R7" t="n">
-        <v>7092369</v>
+        <v>7092322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mycket</t>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1330,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121328022</v>
+        <v>121327930</v>
       </c>
       <c r="B8" t="n">
-        <v>79723</v>
+        <v>79689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711065</v>
+        <v>711183</v>
       </c>
       <c r="R8" t="n">
-        <v>7092292</v>
+        <v>7092303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327901</v>
+        <v>121328034</v>
       </c>
       <c r="B9" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711229</v>
+        <v>711092</v>
       </c>
       <c r="R9" t="n">
-        <v>7092331</v>
+        <v>7092202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,11 +1533,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327981</v>
+        <v>121327967</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,31 +1576,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711115</v>
+        <v>711127</v>
       </c>
       <c r="R10" t="n">
-        <v>7092280</v>
+        <v>7092343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,6 +1647,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327925</v>
+        <v>121327907</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711199</v>
+        <v>711207</v>
       </c>
       <c r="R11" t="n">
-        <v>7092314</v>
+        <v>7092387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121328034</v>
+        <v>121327911</v>
       </c>
       <c r="B12" t="n">
-        <v>79688</v>
+        <v>94771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,30 +1788,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2166</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1828,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711092</v>
+        <v>711178</v>
       </c>
       <c r="R12" t="n">
-        <v>7092202</v>
+        <v>7092396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327839</v>
+        <v>121327941</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,26 +1899,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1934,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711259</v>
+        <v>711196</v>
       </c>
       <c r="R13" t="n">
-        <v>7092208</v>
+        <v>7092277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1975,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327911</v>
+        <v>121327974</v>
       </c>
       <c r="B14" t="n">
-        <v>94765</v>
+        <v>79689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,31 +2005,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2166</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711178</v>
+        <v>711057</v>
       </c>
       <c r="R14" t="n">
-        <v>7092396</v>
+        <v>7092348</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121328016</v>
+        <v>121328046</v>
       </c>
       <c r="B15" t="n">
-        <v>82391</v>
+        <v>57508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,26 +2115,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711061</v>
+        <v>711126</v>
       </c>
       <c r="R15" t="n">
-        <v>7092314</v>
+        <v>7092192</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2210,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121328042</v>
+        <v>121327847</v>
       </c>
       <c r="B16" t="n">
-        <v>82391</v>
+        <v>82392</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711107</v>
+        <v>711262</v>
       </c>
       <c r="R16" t="n">
-        <v>7092184</v>
+        <v>7092221</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327847</v>
+        <v>121327883</v>
       </c>
       <c r="B17" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,26 +2331,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711262</v>
+        <v>711243</v>
       </c>
       <c r="R17" t="n">
-        <v>7092221</v>
+        <v>7092325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2407,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2422,10 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327967</v>
+        <v>121327981</v>
       </c>
       <c r="B18" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,26 +2441,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2465,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711127</v>
+        <v>711115</v>
       </c>
       <c r="R18" t="n">
-        <v>7092343</v>
+        <v>7092280</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,7 +2517,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2528,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327951</v>
+        <v>121327925</v>
       </c>
       <c r="B19" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2544,26 +2551,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2571,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711211</v>
+        <v>711199</v>
       </c>
       <c r="R19" t="n">
-        <v>7092255</v>
+        <v>7092314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2627,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2634,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327907</v>
+        <v>121327892</v>
       </c>
       <c r="B20" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711207</v>
+        <v>711222</v>
       </c>
       <c r="R20" t="n">
-        <v>7092387</v>
+        <v>7092349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327892</v>
+        <v>121328022</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>79724</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2756,35 +2767,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2792,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711222</v>
+        <v>711065</v>
       </c>
       <c r="R21" t="n">
-        <v>7092349</v>
+        <v>7092292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,6 +2842,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2854,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327883</v>
+        <v>121328016</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>82392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,31 +2877,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2902,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711243</v>
+        <v>711061</v>
       </c>
       <c r="R22" t="n">
-        <v>7092325</v>
+        <v>7092314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2946,6 +2948,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327930</v>
+        <v>121327839</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,21 +2983,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3007,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711183</v>
+        <v>711259</v>
       </c>
       <c r="R23" t="n">
-        <v>7092303</v>
+        <v>7092208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3070,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327974</v>
+        <v>121327951</v>
       </c>
       <c r="B24" t="n">
-        <v>79688</v>
+        <v>82392</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,21 +3089,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3113,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711057</v>
+        <v>711211</v>
       </c>
       <c r="R24" t="n">
-        <v>7092348</v>
+        <v>7092255</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327941</v>
+        <v>121328042</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>82392</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,31 +3195,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3224,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711196</v>
+        <v>711107</v>
       </c>
       <c r="R25" t="n">
-        <v>7092277</v>
+        <v>7092184</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,6 +3266,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3286,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121328046</v>
+        <v>121327901</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>79718</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,35 +3297,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3334,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711126</v>
+        <v>711229</v>
       </c>
       <c r="R26" t="n">
-        <v>7092192</v>
+        <v>7092331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,12 +3366,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1993,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327974</v>
+        <v>121328046</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>57508</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,26 +2009,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2036,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711057</v>
+        <v>711126</v>
       </c>
       <c r="R14" t="n">
-        <v>7092348</v>
+        <v>7092192</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2085,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2099,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121328046</v>
+        <v>121327974</v>
       </c>
       <c r="B15" t="n">
-        <v>57508</v>
+        <v>79689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,31 +2119,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2147,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711126</v>
+        <v>711057</v>
       </c>
       <c r="R15" t="n">
-        <v>7092192</v>
+        <v>7092348</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,6 +2190,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327930</v>
+        <v>121327941</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,26 +1364,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711183</v>
+        <v>711196</v>
       </c>
       <c r="R8" t="n">
-        <v>7092303</v>
+        <v>7092277</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121328034</v>
+        <v>121327883</v>
       </c>
       <c r="B9" t="n">
-        <v>79689</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,26 +1474,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711092</v>
+        <v>711243</v>
       </c>
       <c r="R9" t="n">
-        <v>7092202</v>
+        <v>7092325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1550,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1560,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327967</v>
+        <v>121328046</v>
       </c>
       <c r="B10" t="n">
-        <v>90737</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,26 +1584,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1603,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711127</v>
+        <v>711126</v>
       </c>
       <c r="R10" t="n">
-        <v>7092343</v>
+        <v>7092192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,7 +1660,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327907</v>
+        <v>121328034</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,31 +1694,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711207</v>
+        <v>711092</v>
       </c>
       <c r="R11" t="n">
-        <v>7092387</v>
+        <v>7092202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,6 +1765,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327911</v>
+        <v>121327847</v>
       </c>
       <c r="B12" t="n">
-        <v>94771</v>
+        <v>82393</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,31 +1796,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2166</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1820,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711178</v>
+        <v>711262</v>
       </c>
       <c r="R12" t="n">
-        <v>7092396</v>
+        <v>7092221</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327941</v>
+        <v>121328022</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>79725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,35 +1902,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1931,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711196</v>
+        <v>711065</v>
       </c>
       <c r="R13" t="n">
-        <v>7092277</v>
+        <v>7092292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,6 +1977,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1993,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121328046</v>
+        <v>121327925</v>
       </c>
       <c r="B14" t="n">
-        <v>57508</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,31 +2012,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2041,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711126</v>
+        <v>711199</v>
       </c>
       <c r="R14" t="n">
-        <v>7092192</v>
+        <v>7092314</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327974</v>
+        <v>121327901</v>
       </c>
       <c r="B15" t="n">
-        <v>79689</v>
+        <v>79719</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,25 +2118,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711057</v>
+        <v>711229</v>
       </c>
       <c r="R15" t="n">
-        <v>7092348</v>
+        <v>7092331</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,6 +2185,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2217,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327847</v>
+        <v>121327907</v>
       </c>
       <c r="B16" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,26 +2233,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2252,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711262</v>
+        <v>711207</v>
       </c>
       <c r="R16" t="n">
-        <v>7092221</v>
+        <v>7092387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2309,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327883</v>
+        <v>121327839</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,31 +2343,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2363,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711243</v>
+        <v>711259</v>
       </c>
       <c r="R17" t="n">
-        <v>7092325</v>
+        <v>7092208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,6 +2414,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2425,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327981</v>
+        <v>121327930</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,31 +2449,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2473,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711115</v>
+        <v>711183</v>
       </c>
       <c r="R18" t="n">
-        <v>7092280</v>
+        <v>7092303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,6 +2520,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2535,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327925</v>
+        <v>121327974</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,31 +2555,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2583,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711199</v>
+        <v>711057</v>
       </c>
       <c r="R19" t="n">
-        <v>7092314</v>
+        <v>7092348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,6 +2626,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327892</v>
+        <v>121328042</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>82393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,31 +2661,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2693,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711222</v>
+        <v>711107</v>
       </c>
       <c r="R20" t="n">
-        <v>7092349</v>
+        <v>7092184</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,6 +2732,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2755,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121328022</v>
+        <v>121328016</v>
       </c>
       <c r="B21" t="n">
-        <v>79724</v>
+        <v>82393</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,25 +2763,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711065</v>
+        <v>711061</v>
       </c>
       <c r="R21" t="n">
-        <v>7092292</v>
+        <v>7092314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121328016</v>
+        <v>121327981</v>
       </c>
       <c r="B22" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2877,26 +2873,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2904,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711061</v>
+        <v>711115</v>
       </c>
       <c r="R22" t="n">
-        <v>7092314</v>
+        <v>7092280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,7 +2949,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2967,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327839</v>
+        <v>121327892</v>
       </c>
       <c r="B23" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,26 +2983,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711259</v>
+        <v>711222</v>
       </c>
       <c r="R23" t="n">
-        <v>7092208</v>
+        <v>7092349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,7 +3059,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3076,7 +3080,7 @@
         <v>121327951</v>
       </c>
       <c r="B24" t="n">
-        <v>82392</v>
+        <v>82393</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121328042</v>
+        <v>121327911</v>
       </c>
       <c r="B25" t="n">
-        <v>82392</v>
+        <v>94772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,30 +3195,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3222,10 +3227,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711107</v>
+        <v>711178</v>
       </c>
       <c r="R25" t="n">
-        <v>7092184</v>
+        <v>7092396</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327901</v>
+        <v>121327967</v>
       </c>
       <c r="B26" t="n">
-        <v>79718</v>
+        <v>90738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,10 +3333,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711229</v>
+        <v>711127</v>
       </c>
       <c r="R26" t="n">
-        <v>7092331</v>
+        <v>7092343</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3364,11 +3369,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327941</v>
+        <v>121327951</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,31 +1364,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711196</v>
+        <v>711211</v>
       </c>
       <c r="R8" t="n">
-        <v>7092277</v>
+        <v>7092255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,6 +1435,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327883</v>
+        <v>121327907</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1506,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711243</v>
+        <v>711207</v>
       </c>
       <c r="R9" t="n">
-        <v>7092325</v>
+        <v>7092387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121328046</v>
+        <v>121327967</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,31 +1580,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711126</v>
+        <v>711127</v>
       </c>
       <c r="R10" t="n">
-        <v>7092192</v>
+        <v>7092343</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,6 +1651,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1678,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121328034</v>
+        <v>121328016</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,21 +1686,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1721,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711092</v>
+        <v>711061</v>
       </c>
       <c r="R11" t="n">
-        <v>7092202</v>
+        <v>7092314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327847</v>
+        <v>121327974</v>
       </c>
       <c r="B12" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711262</v>
+        <v>711057</v>
       </c>
       <c r="R12" t="n">
-        <v>7092221</v>
+        <v>7092348</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121328022</v>
+        <v>121327981</v>
       </c>
       <c r="B13" t="n">
-        <v>79725</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,30 +1894,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1933,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711065</v>
+        <v>711115</v>
       </c>
       <c r="R13" t="n">
-        <v>7092292</v>
+        <v>7092280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1974,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,7 +1992,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327925</v>
+        <v>121327883</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2044,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711199</v>
+        <v>711243</v>
       </c>
       <c r="R14" t="n">
-        <v>7092314</v>
+        <v>7092325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,10 +2102,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327901</v>
+        <v>121328034</v>
       </c>
       <c r="B15" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,25 +2114,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711229</v>
+        <v>711092</v>
       </c>
       <c r="R15" t="n">
-        <v>7092331</v>
+        <v>7092202</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,11 +2181,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327907</v>
+        <v>121327911</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>94772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,35 +2220,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2265,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711207</v>
+        <v>711178</v>
       </c>
       <c r="R16" t="n">
-        <v>7092387</v>
+        <v>7092396</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2309,6 +2296,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327839</v>
+        <v>121327930</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711259</v>
+        <v>711183</v>
       </c>
       <c r="R17" t="n">
-        <v>7092208</v>
+        <v>7092303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327930</v>
+        <v>121327839</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2476,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711183</v>
+        <v>711259</v>
       </c>
       <c r="R18" t="n">
-        <v>7092303</v>
+        <v>7092208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327974</v>
+        <v>121328042</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,21 +2543,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711057</v>
+        <v>711107</v>
       </c>
       <c r="R19" t="n">
-        <v>7092348</v>
+        <v>7092184</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,7 +2633,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121328042</v>
+        <v>121327847</v>
       </c>
       <c r="B20" t="n">
         <v>82393</v>
@@ -2688,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711107</v>
+        <v>711262</v>
       </c>
       <c r="R20" t="n">
-        <v>7092184</v>
+        <v>7092221</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121328016</v>
+        <v>121327892</v>
       </c>
       <c r="B21" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,26 +2755,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2794,10 +2787,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711061</v>
+        <v>711222</v>
       </c>
       <c r="R21" t="n">
-        <v>7092314</v>
+        <v>7092349</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,7 +2831,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2857,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327981</v>
+        <v>121327901</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,35 +2861,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2905,10 +2892,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711115</v>
+        <v>711229</v>
       </c>
       <c r="R22" t="n">
-        <v>7092280</v>
+        <v>7092331</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,12 +2930,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2967,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327892</v>
+        <v>121328022</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>79725</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,35 +2972,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3015,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711222</v>
+        <v>711065</v>
       </c>
       <c r="R23" t="n">
-        <v>7092349</v>
+        <v>7092292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,6 +3047,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3077,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327951</v>
+        <v>121327925</v>
       </c>
       <c r="B24" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,26 +3082,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3120,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711211</v>
+        <v>711199</v>
       </c>
       <c r="R24" t="n">
-        <v>7092255</v>
+        <v>7092314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,7 +3158,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3183,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327911</v>
+        <v>121328046</v>
       </c>
       <c r="B25" t="n">
-        <v>94772</v>
+        <v>57509</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3195,31 +3188,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2166</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lindb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3227,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711178</v>
+        <v>711126</v>
       </c>
       <c r="R25" t="n">
-        <v>7092396</v>
+        <v>7092192</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3268,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3290,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327967</v>
+        <v>121327941</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,26 +3302,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3333,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711127</v>
+        <v>711196</v>
       </c>
       <c r="R26" t="n">
-        <v>7092343</v>
+        <v>7092277</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3378,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327951</v>
+        <v>121328022</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>79725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711211</v>
+        <v>711065</v>
       </c>
       <c r="R8" t="n">
-        <v>7092255</v>
+        <v>7092292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327907</v>
+        <v>121328046</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,31 +1470,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711207</v>
+        <v>711126</v>
       </c>
       <c r="R9" t="n">
-        <v>7092387</v>
+        <v>7092192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327967</v>
+        <v>121327883</v>
       </c>
       <c r="B10" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,26 +1580,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1607,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711127</v>
+        <v>711243</v>
       </c>
       <c r="R10" t="n">
-        <v>7092343</v>
+        <v>7092325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1656,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121328016</v>
+        <v>121327981</v>
       </c>
       <c r="B11" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,26 +1690,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1713,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711061</v>
+        <v>711115</v>
       </c>
       <c r="R11" t="n">
-        <v>7092314</v>
+        <v>7092280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,7 +1766,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1776,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327974</v>
+        <v>121327911</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>94772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,30 +1796,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2166</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1819,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711057</v>
+        <v>711178</v>
       </c>
       <c r="R12" t="n">
-        <v>7092348</v>
+        <v>7092396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327981</v>
+        <v>121328042</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,31 +1907,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1930,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711115</v>
+        <v>711107</v>
       </c>
       <c r="R13" t="n">
-        <v>7092280</v>
+        <v>7092184</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,6 +1978,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327883</v>
+        <v>121327930</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,31 +2013,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711243</v>
+        <v>711183</v>
       </c>
       <c r="R14" t="n">
-        <v>7092325</v>
+        <v>7092303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,6 +2084,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2102,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121328034</v>
+        <v>121327847</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2145,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711092</v>
+        <v>711262</v>
       </c>
       <c r="R15" t="n">
-        <v>7092202</v>
+        <v>7092221</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327911</v>
+        <v>121327892</v>
       </c>
       <c r="B16" t="n">
-        <v>94772</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,31 +2221,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2166</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2252,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711178</v>
+        <v>711222</v>
       </c>
       <c r="R16" t="n">
-        <v>7092396</v>
+        <v>7092349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2301,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327930</v>
+        <v>121327839</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,21 +2335,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711183</v>
+        <v>711259</v>
       </c>
       <c r="R17" t="n">
-        <v>7092303</v>
+        <v>7092208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2421,10 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327839</v>
+        <v>121327951</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,21 +2441,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2464,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711259</v>
+        <v>711211</v>
       </c>
       <c r="R18" t="n">
-        <v>7092208</v>
+        <v>7092255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328042</v>
+        <v>121328034</v>
       </c>
       <c r="B19" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2543,21 +2547,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711107</v>
+        <v>711092</v>
       </c>
       <c r="R19" t="n">
-        <v>7092184</v>
+        <v>7092202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327847</v>
+        <v>121327941</v>
       </c>
       <c r="B20" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2649,26 +2653,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2676,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711262</v>
+        <v>711196</v>
       </c>
       <c r="R20" t="n">
-        <v>7092221</v>
+        <v>7092277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,7 +2729,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2739,7 +2747,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327892</v>
+        <v>121327925</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2787,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711222</v>
+        <v>711199</v>
       </c>
       <c r="R21" t="n">
-        <v>7092349</v>
+        <v>7092314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2849,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327901</v>
+        <v>121327967</v>
       </c>
       <c r="B22" t="n">
-        <v>79719</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,25 +2869,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2892,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711229</v>
+        <v>711127</v>
       </c>
       <c r="R22" t="n">
-        <v>7092331</v>
+        <v>7092343</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,11 +2936,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121328022</v>
+        <v>121328016</v>
       </c>
       <c r="B23" t="n">
-        <v>79725</v>
+        <v>82393</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2972,25 +2975,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711065</v>
+        <v>711061</v>
       </c>
       <c r="R23" t="n">
-        <v>7092292</v>
+        <v>7092314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327925</v>
+        <v>121327974</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,31 +3085,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3114,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711199</v>
+        <v>711057</v>
       </c>
       <c r="R24" t="n">
-        <v>7092314</v>
+        <v>7092348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,6 +3156,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3176,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121328046</v>
+        <v>121327907</v>
       </c>
       <c r="B25" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,31 +3191,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3224,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711126</v>
+        <v>711207</v>
       </c>
       <c r="R25" t="n">
-        <v>7092192</v>
+        <v>7092387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327941</v>
+        <v>121327901</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,35 +3297,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3334,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711196</v>
+        <v>711229</v>
       </c>
       <c r="R26" t="n">
-        <v>7092277</v>
+        <v>7092331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,12 +3366,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121328022</v>
+        <v>121327925</v>
       </c>
       <c r="B8" t="n">
-        <v>79725</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,30 +1360,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711065</v>
+        <v>711199</v>
       </c>
       <c r="R8" t="n">
-        <v>7092292</v>
+        <v>7092314</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121328046</v>
+        <v>121327892</v>
       </c>
       <c r="B9" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,31 +1474,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711126</v>
+        <v>711222</v>
       </c>
       <c r="R9" t="n">
-        <v>7092192</v>
+        <v>7092349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327883</v>
+        <v>121327901</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,35 +1580,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1612,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711243</v>
+        <v>711229</v>
       </c>
       <c r="R10" t="n">
-        <v>7092325</v>
+        <v>7092331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,12 +1649,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1674,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327981</v>
+        <v>121327839</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,31 +1695,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711115</v>
+        <v>711259</v>
       </c>
       <c r="R11" t="n">
-        <v>7092280</v>
+        <v>7092208</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1784,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121327911</v>
+        <v>121328042</v>
       </c>
       <c r="B12" t="n">
-        <v>94772</v>
+        <v>82393</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,31 +1797,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2166</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711178</v>
+        <v>711107</v>
       </c>
       <c r="R12" t="n">
-        <v>7092396</v>
+        <v>7092184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121328042</v>
+        <v>121327930</v>
       </c>
       <c r="B13" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711107</v>
+        <v>711183</v>
       </c>
       <c r="R13" t="n">
-        <v>7092184</v>
+        <v>7092303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327930</v>
+        <v>121327847</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711183</v>
+        <v>711262</v>
       </c>
       <c r="R14" t="n">
-        <v>7092303</v>
+        <v>7092221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327847</v>
+        <v>121327974</v>
       </c>
       <c r="B15" t="n">
-        <v>82393</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711262</v>
+        <v>711057</v>
       </c>
       <c r="R15" t="n">
-        <v>7092221</v>
+        <v>7092348</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327892</v>
+        <v>121327967</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,31 +2225,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711222</v>
+        <v>711127</v>
       </c>
       <c r="R16" t="n">
-        <v>7092349</v>
+        <v>7092343</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,6 +2296,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2319,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327839</v>
+        <v>121327951</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711259</v>
+        <v>711211</v>
       </c>
       <c r="R17" t="n">
-        <v>7092208</v>
+        <v>7092255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327951</v>
+        <v>121327911</v>
       </c>
       <c r="B18" t="n">
-        <v>82393</v>
+        <v>94772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,30 +2433,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2468,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711211</v>
+        <v>711178</v>
       </c>
       <c r="R18" t="n">
-        <v>7092255</v>
+        <v>7092396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328034</v>
+        <v>121328046</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>57509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,26 +2544,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2574,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711092</v>
+        <v>711126</v>
       </c>
       <c r="R19" t="n">
-        <v>7092202</v>
+        <v>7092192</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,7 +2620,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2747,7 +2748,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327925</v>
+        <v>121327883</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2795,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711199</v>
+        <v>711243</v>
       </c>
       <c r="R21" t="n">
-        <v>7092314</v>
+        <v>7092325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327967</v>
+        <v>121328016</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>82393</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,21 +2874,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711127</v>
+        <v>711061</v>
       </c>
       <c r="R22" t="n">
-        <v>7092343</v>
+        <v>7092314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121328016</v>
+        <v>121327907</v>
       </c>
       <c r="B23" t="n">
-        <v>82393</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,26 +2980,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3006,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711061</v>
+        <v>711207</v>
       </c>
       <c r="R23" t="n">
-        <v>7092314</v>
+        <v>7092387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3050,7 +3056,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3069,7 +3074,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327974</v>
+        <v>121328034</v>
       </c>
       <c r="B24" t="n">
         <v>79690</v>
@@ -3112,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711057</v>
+        <v>711092</v>
       </c>
       <c r="R24" t="n">
-        <v>7092348</v>
+        <v>7092202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327907</v>
+        <v>121328022</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>79725</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,35 +3192,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711207</v>
+        <v>711065</v>
       </c>
       <c r="R25" t="n">
-        <v>7092387</v>
+        <v>7092292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3267,6 +3267,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3285,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327901</v>
+        <v>121327981</v>
       </c>
       <c r="B26" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,30 +3298,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3328,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711229</v>
+        <v>711115</v>
       </c>
       <c r="R26" t="n">
-        <v>7092331</v>
+        <v>7092280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,18 +3372,12 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327925</v>
+        <v>121327901</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1360,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711199</v>
+        <v>711229</v>
       </c>
       <c r="R8" t="n">
-        <v>7092314</v>
+        <v>7092331</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,12 +1429,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327892</v>
+        <v>121327925</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1506,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711222</v>
+        <v>711199</v>
       </c>
       <c r="R9" t="n">
-        <v>7092349</v>
+        <v>7092314</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327901</v>
+        <v>121327892</v>
       </c>
       <c r="B10" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,30 +1581,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711229</v>
+        <v>711222</v>
       </c>
       <c r="R10" t="n">
-        <v>7092331</v>
+        <v>7092349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,18 +1655,12 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327911</v>
+        <v>121328046</v>
       </c>
       <c r="B18" t="n">
-        <v>94772</v>
+        <v>57509</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,31 +2433,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2166</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lindb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2465,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711178</v>
+        <v>711126</v>
       </c>
       <c r="R18" t="n">
-        <v>7092396</v>
+        <v>7092192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,7 +2513,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2528,10 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328046</v>
+        <v>121327911</v>
       </c>
       <c r="B19" t="n">
-        <v>57509</v>
+        <v>94772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2540,35 +2543,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>2166</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2576,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711126</v>
+        <v>711178</v>
       </c>
       <c r="R19" t="n">
-        <v>7092192</v>
+        <v>7092396</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2620,6 +2619,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327907</v>
+        <v>121328034</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,31 +2980,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711207</v>
+        <v>711092</v>
       </c>
       <c r="R23" t="n">
-        <v>7092387</v>
+        <v>7092202</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,6 +3051,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3074,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121328034</v>
+        <v>121327907</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,26 +3086,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711092</v>
+        <v>711207</v>
       </c>
       <c r="R24" t="n">
-        <v>7092202</v>
+        <v>7092387</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3161,7 +3162,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327901</v>
+        <v>121327925</v>
       </c>
       <c r="B8" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,30 +1360,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711229</v>
+        <v>711199</v>
       </c>
       <c r="R8" t="n">
-        <v>7092331</v>
+        <v>7092314</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,18 +1434,12 @@
           <t>2024-11-24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1459,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327925</v>
+        <v>121327892</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1507,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711199</v>
+        <v>711222</v>
       </c>
       <c r="R9" t="n">
-        <v>7092314</v>
+        <v>7092349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327892</v>
+        <v>121327901</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,35 +1580,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711222</v>
+        <v>711229</v>
       </c>
       <c r="R10" t="n">
-        <v>7092349</v>
+        <v>7092331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,12 +1649,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121328046</v>
+        <v>121327911</v>
       </c>
       <c r="B18" t="n">
-        <v>57509</v>
+        <v>94772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,35 +2433,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>2166</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2469,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711126</v>
+        <v>711178</v>
       </c>
       <c r="R18" t="n">
-        <v>7092192</v>
+        <v>7092396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,6 +2509,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2531,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121327911</v>
+        <v>121328046</v>
       </c>
       <c r="B19" t="n">
-        <v>94772</v>
+        <v>57509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2543,31 +2540,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2166</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lindb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2575,10 +2576,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711178</v>
+        <v>711126</v>
       </c>
       <c r="R19" t="n">
-        <v>7092396</v>
+        <v>7092192</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,7 +2620,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121328034</v>
+        <v>121327907</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,26 +2980,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711092</v>
+        <v>711207</v>
       </c>
       <c r="R23" t="n">
-        <v>7092202</v>
+        <v>7092387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,7 +3056,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3070,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121327907</v>
+        <v>121328034</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,31 +3090,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3118,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711207</v>
+        <v>711092</v>
       </c>
       <c r="R24" t="n">
-        <v>7092387</v>
+        <v>7092202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3162,6 +3161,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327925</v>
+        <v>121327901</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1360,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711199</v>
+        <v>711229</v>
       </c>
       <c r="R8" t="n">
-        <v>7092314</v>
+        <v>7092331</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,12 +1429,18 @@
           <t>2024-11-24</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327892</v>
+        <v>121327907</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711222</v>
+        <v>711207</v>
       </c>
       <c r="R9" t="n">
-        <v>7092349</v>
+        <v>7092387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327901</v>
+        <v>121327951</v>
       </c>
       <c r="B10" t="n">
-        <v>79719</v>
+        <v>82400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,25 +1581,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711229</v>
+        <v>711211</v>
       </c>
       <c r="R10" t="n">
-        <v>7092331</v>
+        <v>7092255</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,11 +1648,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327839</v>
+        <v>121327883</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,26 +1691,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711259</v>
+        <v>711243</v>
       </c>
       <c r="R11" t="n">
-        <v>7092208</v>
+        <v>7092325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121328042</v>
+        <v>121328016</v>
       </c>
       <c r="B12" t="n">
-        <v>82393</v>
+        <v>82400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711107</v>
+        <v>711061</v>
       </c>
       <c r="R12" t="n">
-        <v>7092184</v>
+        <v>7092314</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327930</v>
+        <v>121327967</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>90746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711183</v>
+        <v>711127</v>
       </c>
       <c r="R13" t="n">
-        <v>7092303</v>
+        <v>7092343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327847</v>
+        <v>121327974</v>
       </c>
       <c r="B14" t="n">
-        <v>82393</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711262</v>
+        <v>711057</v>
       </c>
       <c r="R14" t="n">
-        <v>7092221</v>
+        <v>7092348</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121327974</v>
+        <v>121328042</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>82400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711057</v>
+        <v>711107</v>
       </c>
       <c r="R15" t="n">
-        <v>7092348</v>
+        <v>7092184</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327967</v>
+        <v>121327892</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,26 +2225,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2252,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711127</v>
+        <v>711222</v>
       </c>
       <c r="R16" t="n">
-        <v>7092343</v>
+        <v>7092349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2301,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121327951</v>
+        <v>121328022</v>
       </c>
       <c r="B17" t="n">
-        <v>82393</v>
+        <v>79732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2327,25 +2331,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711211</v>
+        <v>711065</v>
       </c>
       <c r="R17" t="n">
-        <v>7092255</v>
+        <v>7092292</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2421,10 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327911</v>
+        <v>121327925</v>
       </c>
       <c r="B18" t="n">
-        <v>94772</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,31 +2437,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2166</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2465,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711178</v>
+        <v>711199</v>
       </c>
       <c r="R18" t="n">
-        <v>7092396</v>
+        <v>7092314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,7 +2517,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2531,7 +2538,7 @@
         <v>121328046</v>
       </c>
       <c r="B19" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327941</v>
+        <v>121327930</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>79697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,31 +2661,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2686,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711196</v>
+        <v>711183</v>
       </c>
       <c r="R20" t="n">
-        <v>7092277</v>
+        <v>7092303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,6 +2732,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2748,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327883</v>
+        <v>121327847</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>82400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2764,31 +2767,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2796,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711243</v>
+        <v>711262</v>
       </c>
       <c r="R21" t="n">
-        <v>7092325</v>
+        <v>7092221</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,6 +2838,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2858,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121328016</v>
+        <v>121327941</v>
       </c>
       <c r="B22" t="n">
-        <v>82393</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,26 +2873,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711061</v>
+        <v>711196</v>
       </c>
       <c r="R22" t="n">
-        <v>7092314</v>
+        <v>7092277</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2945,7 +2949,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327907</v>
+        <v>121327981</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,7 +3005,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3012,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711207</v>
+        <v>711115</v>
       </c>
       <c r="R23" t="n">
-        <v>7092387</v>
+        <v>7092280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,7 +3080,7 @@
         <v>121328034</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121328022</v>
+        <v>121327839</v>
       </c>
       <c r="B25" t="n">
-        <v>79725</v>
+        <v>90728</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3195,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3223,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711065</v>
+        <v>711259</v>
       </c>
       <c r="R25" t="n">
-        <v>7092292</v>
+        <v>7092208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327981</v>
+        <v>121327911</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>94780</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,35 +3301,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2166</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3334,10 +3333,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711115</v>
+        <v>711178</v>
       </c>
       <c r="R26" t="n">
-        <v>7092280</v>
+        <v>7092396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3378,6 +3377,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>121332618</v>
       </c>
       <c r="B27" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -2751,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327847</v>
+        <v>121327941</v>
       </c>
       <c r="B21" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,26 +2767,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2794,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711262</v>
+        <v>711196</v>
       </c>
       <c r="R21" t="n">
-        <v>7092221</v>
+        <v>7092277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,7 +2843,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2857,7 +2861,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327941</v>
+        <v>121327981</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2905,10 +2909,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711196</v>
+        <v>711115</v>
       </c>
       <c r="R22" t="n">
-        <v>7092277</v>
+        <v>7092280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2967,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327981</v>
+        <v>121327847</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,31 +2987,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3015,10 +3014,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711115</v>
+        <v>711262</v>
       </c>
       <c r="R23" t="n">
-        <v>7092280</v>
+        <v>7092221</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,6 +3058,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3500,6 +3500,610 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133851025</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91940</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>711062</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7092226</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133850938</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>711049</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7092340</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-39</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133851061</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>711148</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7092143</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-83</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133850943</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>711068</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7092212</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-34</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133851041</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91940</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>711096</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7092308</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-33</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133851127</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>711063</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7092233</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3500,610 +3500,6 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>133851025</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91940</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Skogen, Ång</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>711062</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7092226</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-49</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>133850938</v>
-      </c>
-      <c r="B29" t="n">
-        <v>80439</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Skogen, Ång</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>711049</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7092340</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-39</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>133851061</v>
-      </c>
-      <c r="B30" t="n">
-        <v>79334</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Skogen, Ång</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>711148</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7092143</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-83</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>133850943</v>
-      </c>
-      <c r="B31" t="n">
-        <v>80439</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Skogen, Ång</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>711068</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7092212</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-34</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>133851041</v>
-      </c>
-      <c r="B32" t="n">
-        <v>91940</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Skogen, Ång</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>711096</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7092308</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-33</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>133851127</v>
-      </c>
-      <c r="B33" t="n">
-        <v>8444</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Skogen, Ång</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>711063</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7092233</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121172820</v>
+        <v>121327839</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711081</v>
+        <v>711259</v>
       </c>
       <c r="R2" t="n">
-        <v>7092245</v>
+        <v>7092208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på sälg</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121172849</v>
+        <v>121332618</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,31 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711238</v>
+        <v>711255</v>
       </c>
       <c r="R3" t="n">
-        <v>7092305</v>
+        <v>7092199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,33 +858,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Severin Suess</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Severin Suess, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121173021</v>
+        <v>121327847</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711216</v>
+        <v>711262</v>
       </c>
       <c r="R4" t="n">
-        <v>7092369</v>
+        <v>7092221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,17 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121173043</v>
+        <v>121327951</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,31 +989,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711192</v>
+        <v>711211</v>
       </c>
       <c r="R5" t="n">
-        <v>7092394</v>
+        <v>7092255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,17 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,6 +1060,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121172744</v>
+        <v>121328016</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711136</v>
+        <v>711061</v>
       </c>
       <c r="R6" t="n">
-        <v>7092251</v>
+        <v>7092314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,17 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,47 +1180,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121173036</v>
+        <v>121328042</v>
       </c>
       <c r="B7" t="n">
-        <v>57466</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711181</v>
+        <v>711107</v>
       </c>
       <c r="R7" t="n">
-        <v>7092322</v>
+        <v>7092184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,17 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst två</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,6 +1262,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121327901</v>
+        <v>121327911</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,26 +1292,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2166</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711229</v>
+        <v>711178</v>
       </c>
       <c r="R8" t="n">
-        <v>7092331</v>
+        <v>7092396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,11 +1356,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,47 +1383,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121327907</v>
+        <v>121172744</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711207</v>
+        <v>711136</v>
       </c>
       <c r="R9" t="n">
-        <v>7092387</v>
+        <v>7092251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,12 +1451,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,6 +1470,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121327951</v>
+        <v>121172820</v>
       </c>
       <c r="B10" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,21 +1500,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711211</v>
+        <v>711081</v>
       </c>
       <c r="R10" t="n">
-        <v>7092255</v>
+        <v>7092245</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,12 +1557,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,15 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121327883</v>
+        <v>121173021</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,31 +1606,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711243</v>
+        <v>711216</v>
       </c>
       <c r="R11" t="n">
-        <v>7092325</v>
+        <v>7092369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1663,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,6 +1682,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1785,15 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121328016</v>
+        <v>121327930</v>
       </c>
       <c r="B12" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711061</v>
+        <v>711183</v>
       </c>
       <c r="R12" t="n">
-        <v>7092314</v>
+        <v>7092303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,15 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121327967</v>
+        <v>121327974</v>
       </c>
       <c r="B13" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711127</v>
+        <v>711057</v>
       </c>
       <c r="R13" t="n">
-        <v>7092343</v>
+        <v>7092348</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,15 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121327974</v>
+        <v>121328034</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711057</v>
+        <v>711092</v>
       </c>
       <c r="R14" t="n">
-        <v>7092348</v>
+        <v>7092202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,37 +2004,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121328042</v>
+        <v>121327901</v>
       </c>
       <c r="B15" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>711107</v>
+        <v>711229</v>
       </c>
       <c r="R15" t="n">
-        <v>7092184</v>
+        <v>7092331</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,6 +2078,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,47 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121327892</v>
+        <v>121328022</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2257,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>711222</v>
+        <v>711065</v>
       </c>
       <c r="R16" t="n">
-        <v>7092349</v>
+        <v>7092292</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,6 +2192,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2319,15 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121328022</v>
+        <v>121172849</v>
       </c>
       <c r="B17" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,26 +2222,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2362,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>711065</v>
+        <v>711238</v>
       </c>
       <c r="R17" t="n">
-        <v>7092292</v>
+        <v>7092305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,12 +2284,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,7 +2298,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2425,15 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121327925</v>
+        <v>121173043</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,7 +2349,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2473,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>711199</v>
+        <v>711192</v>
       </c>
       <c r="R18" t="n">
-        <v>7092314</v>
+        <v>7092394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,12 +2389,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,15 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121328046</v>
+        <v>121327883</v>
       </c>
       <c r="B19" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,31 +2437,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2583,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>711126</v>
+        <v>711243</v>
       </c>
       <c r="R19" t="n">
-        <v>7092192</v>
+        <v>7092325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,15 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121327930</v>
+        <v>121327892</v>
       </c>
       <c r="B20" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,26 +2542,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2688,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>711183</v>
+        <v>711222</v>
       </c>
       <c r="R20" t="n">
-        <v>7092303</v>
+        <v>7092349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,7 +2618,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2751,15 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121327941</v>
+        <v>121327907</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2669,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2799,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>711196</v>
+        <v>711207</v>
       </c>
       <c r="R21" t="n">
-        <v>7092277</v>
+        <v>7092387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,15 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121327981</v>
+        <v>121327925</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2774,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2909,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>711115</v>
+        <v>711199</v>
       </c>
       <c r="R22" t="n">
-        <v>7092280</v>
+        <v>7092314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,15 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121327847</v>
+        <v>121327941</v>
       </c>
       <c r="B23" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2987,26 +2857,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3014,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>711262</v>
+        <v>711196</v>
       </c>
       <c r="R23" t="n">
-        <v>7092221</v>
+        <v>7092277</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3058,7 +2933,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3077,15 +2951,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121328034</v>
+        <v>121327981</v>
       </c>
       <c r="B24" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,26 +2962,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3120,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>711092</v>
+        <v>711115</v>
       </c>
       <c r="R24" t="n">
-        <v>7092202</v>
+        <v>7092280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,7 +3038,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3183,15 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121327839</v>
+        <v>121328046</v>
       </c>
       <c r="B25" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,26 +3067,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3226,10 +3099,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>711259</v>
+        <v>711126</v>
       </c>
       <c r="R25" t="n">
-        <v>7092208</v>
+        <v>7092192</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3143,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3289,43 +3161,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121327911</v>
+        <v>121173036</v>
       </c>
       <c r="B26" t="n">
-        <v>94780</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2166</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lindb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3333,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>711178</v>
+        <v>711181</v>
       </c>
       <c r="R26" t="n">
-        <v>7092396</v>
+        <v>7092322</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,12 +3234,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst två</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3377,7 +3253,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3393,112 +3268,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>121332618</v>
-      </c>
-      <c r="B27" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Klubbsjöbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>711255</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7092199</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Severin Suess</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Severin Suess, Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51874-2024 artfynd.xlsx
+++ b/artfynd/A 51874-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121332618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121328016</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121328042</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327911</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121172744</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121172820</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173021</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327930</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327974</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121328034</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,6 +2177,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327901</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121328022</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121172849</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173043</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2528,6 +2618,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327883</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327892</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327907</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2843,6 +2948,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327925</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2948,6 +3058,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327941</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3053,6 +3168,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121327981</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3158,6 +3278,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121328046</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3268,8 +3393,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121173036</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>